--- a/Data/MemoryFragment.xlsx
+++ b/Data/MemoryFragment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="585" windowWidth="27735" windowHeight="12825" activeTab="1"/>
+    <workbookView xWindow="630" yWindow="585" windowWidth="27735" windowHeight="12825"/>
   </bookViews>
   <sheets>
     <sheet name="MemoryFragmentBase" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
   <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="UzW0sF8QQMiyVH7b+4ukUx1xU6FT8CDhgOs9hiGz+q4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="" roundtripDataChecksum="UzW0sF8QQMiyVH7b+4ukUx1xU6FT8CDhgOs9hiGz+q4="/>
     </ext>
   </extLst>
 </workbook>
@@ -769,7 +769,7 @@
   <dimension ref="A1:H912"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" customWidth="1"/>
     <col min="4" max="26" width="11" customWidth="1"/>
@@ -2899,7 +2899,7 @@
   <dimension ref="A1:G1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.42578125" customWidth="1"/>
     <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.140625" customWidth="1"/>
